--- a/site/Dayforce-to-Active-Directory-Multidomain/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-Multidomain/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,29 +727,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Custom Password Policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KADF7R30RFKMHY0T79EWCRN3</t>
+          <t>h_01KHQP1PV9JMN083DBZQP2BAAM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KADF7R30RFKMHY0T79EWCRN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP1PV9JMN083DBZQP2BAAM</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
+          <t>h_01KADF7R30RFKMHY0T79EWCRN3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KADF7R30RFKMHY0T79EWCRN3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Setting</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,230 +781,362 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KDP15YN0777ANCJA7WNRTTG2</t>
+          <t>h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDP15YN0777ANCJA7WNRTTG2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Termination Settings</t>
+          <t>User Creation Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KDPK17MB1E6W050SNCY9ZE83</t>
+          <t>h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDPK17MB1E6W050SNCY9ZE83</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>User Update Notification Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KAE27MY7T9RFNXTW210MBD6T</t>
+          <t>h_01KHQP2D967DX3PZS9JJV4K64E</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27MY7T9RFNXTW210MBD6T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP2D967DX3PZS9JJV4K64E</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Target Settings</t>
+          <t>User Termination Notification Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
+          <t>h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Success Email Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+          <t>h_01KHQP2PNAJ40RBN5N00H7W881</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP2PNAJ40RBN5N00H7W881</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Failure Email Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+          <t>h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+          <t>h_01KDP15YN0777ANCJA7WNRTTG2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDP15YN0777ANCJA7WNRTTG2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Termination Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KAE29BFPRBFZCTF419GM72K2</t>
+          <t>h_01KDPK17MB1E6W050SNCY9ZE83</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE29BFPRBFZCTF419GM72K2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KDPK17MB1E6W050SNCY9ZE83</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KAE27MY7T9RFNXTW210MBD6T</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27MY7T9RFNXTW210MBD6T</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Target Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KAE29BFPRBFZCTF419GM72K2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01KAE29BFPRBFZCTF419GM72K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-Multidomain/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
